--- a/00 Raw data/SDG/Publications_by_SDG_-_National_Kaohsiung_University_of_Science_and_Technology.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_National_Kaohsiung_University_of_Science_and_Technology.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -209,13 +209,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="D13" t="n">
-        <v>177.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="14">
@@ -228,10 +228,10 @@
         <v>56.0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="D14" t="n">
-        <v>949.0</v>
+        <v>991.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>596.0</v>
+        <v>633.0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="D15" t="n">
-        <v>11758.0</v>
+        <v>13256.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>133.0</v>
+        <v>142.0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="D16" t="n">
-        <v>2068.0</v>
+        <v>2545.0</v>
       </c>
     </row>
     <row r="17">
@@ -289,13 +289,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>342.0</v>
+        <v>356.0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="D18" t="n">
-        <v>10470.0</v>
+        <v>11343.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>805.0</v>
+        <v>862.0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="D19" t="n">
-        <v>18268.0</v>
+        <v>19794.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>327.0</v>
+        <v>340.0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="D20" t="n">
-        <v>7030.0</v>
+        <v>7707.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>911.0</v>
+        <v>973.0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="D21" t="n">
-        <v>17385.0</v>
+        <v>19194.0</v>
       </c>
     </row>
     <row r="22">
@@ -353,13 +353,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53.0</v>
+        <v>57.0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="D22" t="n">
-        <v>322.0</v>
+        <v>370.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>237.0</v>
+        <v>256.0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="D23" t="n">
-        <v>3583.0</v>
+        <v>4438.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>446.0</v>
+        <v>469.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="D24" t="n">
-        <v>11141.0</v>
+        <v>12112.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>293.0</v>
+        <v>305.0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>7006.0</v>
+        <v>7631.0</v>
       </c>
     </row>
     <row r="26">
@@ -417,13 +417,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>383.0</v>
+        <v>407.0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="D26" t="n">
-        <v>7540.0</v>
+        <v>8569.0</v>
       </c>
     </row>
     <row r="27">
@@ -433,13 +433,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="D27" t="n">
-        <v>3884.0</v>
+        <v>4089.0</v>
       </c>
     </row>
     <row r="28">
@@ -449,13 +449,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="C28" t="n">
         <v>0.62</v>
       </c>
       <c r="D28" t="n">
-        <v>285.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3117.0</v>
+        <v>3343.0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="D29" t="n">
-        <v>59518.0</v>
+        <v>67140.0</v>
       </c>
     </row>
     <row r="30">
